--- a/kits/pdf-binder/samples/submittal-package/output/SAMPLE_Submittal_23-74-00-001_R0_RTU-1-index.xlsx
+++ b/kits/pdf-binder/samples/submittal-package/output/SAMPLE_Submittal_23-74-00-001_R0_RTU-1-index.xlsx
@@ -107,7 +107,7 @@
     <t>rtu-480-datasheet.pdf</t>
   </si>
   <si>
-    <t>074f3c1c3272f07ee765d74b2888eb62e2875a4e164da093c30fa8d4a3507918</t>
+    <t>bdeeea00dbb5885ccd481183ff11b6b9b27d1aaf3fae68b141492f2999a6ca07</t>
   </si>
   <si>
     <t>Installation and maintenance manual - chapters 1 and 2</t>
@@ -122,7 +122,7 @@
     <t>3-4</t>
   </si>
   <si>
-    <t>68a36311dffb4190d9fe6b7d0d7a7c26d2adfb29b99a9c96c423303d6766eb0a</t>
+    <t>0063627689d18dabd03425fbe6845a663c63c5a2ed9f2b74c4e94588d3b6a644</t>
   </si>
   <si>
     <t>Manufacturer's warranty terms</t>
@@ -131,7 +131,7 @@
     <t>rtu-1-warranty.pdf</t>
   </si>
   <si>
-    <t>7798802ab615fc7c92c2c255335ffa973a6c8f7792662d0bc333cc02eda04c4a</t>
+    <t>406f9f36396a6c91901c6fb994226d7418efff1e433925f6461b61532bde7175</t>
   </si>
   <si>
     <t>Binder summary</t>
@@ -155,7 +155,7 @@
     <t>Built on</t>
   </si>
   <si>
-    <t>2026-10-07 10:35</t>
+    <t>2026-10-07 10:49</t>
   </si>
   <si>
     <t>Total pages</t>
